--- a/Delhi-July-2025.xlsx
+++ b/Delhi-July-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Delhi</t>
   </si>
   <si>
@@ -106,10 +109,10 @@
     <t>MH02FG7557</t>
   </si>
   <si>
-    <t>DL1NA-3869</t>
-  </si>
-  <si>
-    <t>DL1NA-3910</t>
+    <t>DL1NA3869</t>
+  </si>
+  <si>
+    <t>DL1NA3910</t>
   </si>
   <si>
     <t>HR38AD1176</t>
@@ -130,13 +133,13 @@
     <t>HR38AE5738</t>
   </si>
   <si>
-    <t>HR38Y-6988</t>
-  </si>
-  <si>
-    <t>HR55AR-0857</t>
-  </si>
-  <si>
-    <t>HR55AR-1793</t>
+    <t>HR38Y6988</t>
+  </si>
+  <si>
+    <t>HR55AR0857</t>
+  </si>
+  <si>
+    <t>HR55AR1793</t>
   </si>
   <si>
     <t>MH02ER7925</t>
@@ -172,7 +175,7 @@
     <t>HR55AX6981</t>
   </si>
   <si>
-    <t>DL1N-6505</t>
+    <t>DL1N6505</t>
   </si>
   <si>
     <t>HR38AE9224</t>
@@ -208,13 +211,13 @@
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>Dzire</t>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>ETIOS</t>
@@ -235,31 +238,43 @@
     <t>25/01/2024</t>
   </si>
   <si>
+    <t>17/08/2022</t>
+  </si>
+  <si>
+    <t>21/04/2023</t>
+  </si>
+  <si>
+    <t>16/08/2018</t>
+  </si>
+  <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>21/04/2014</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
+  </si>
+  <si>
+    <t>30/07/2024</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>17/08/2022</t>
-  </si>
-  <si>
-    <t>21/04/2023</t>
-  </si>
-  <si>
-    <t>25/03/2021</t>
-  </si>
-  <si>
-    <t>21/09/2021</t>
-  </si>
-  <si>
-    <t>21/10/2021</t>
-  </si>
-  <si>
-    <t>14/03/2023</t>
-  </si>
-  <si>
-    <t>23/01/2025</t>
-  </si>
-  <si>
-    <t>30/07/2024</t>
   </si>
 </sst>
 </file>
@@ -621,10 +636,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,28 +718,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2">
         <v>50675</v>
@@ -784,24 +802,24 @@
         <v>10.71</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" s="2">
         <v>44748</v>
@@ -864,27 +882,27 @@
         <v>-92.77</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" t="s">
-        <v>73</v>
+        <v>65</v>
+      </c>
+      <c r="G4" s="2">
+        <v>43565</v>
       </c>
       <c r="H4">
         <v>221068</v>
@@ -944,27 +962,27 @@
         <v>54.74</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" t="s">
-        <v>73</v>
+        <v>65</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43565</v>
       </c>
       <c r="H5">
         <v>221028</v>
@@ -1024,24 +1042,24 @@
         <v>55.27</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -1104,24 +1122,24 @@
         <v>52.72</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7" s="2">
         <v>44904</v>
@@ -1184,24 +1202,24 @@
         <v>51.84</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>74</v>
@@ -1264,24 +1282,24 @@
         <v>60.07</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="2">
         <v>44904</v>
@@ -1344,24 +1362,24 @@
         <v>53.79</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>75</v>
@@ -1424,24 +1442,24 @@
         <v>16.53</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
         <v>75</v>
@@ -1504,27 +1522,27 @@
         <v>25.68</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>118410</v>
@@ -1584,27 +1602,27 @@
         <v>78.01000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>83985</v>
@@ -1664,27 +1682,27 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H14">
         <v>100460</v>
@@ -1744,27 +1762,27 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
+        <v>65</v>
+      </c>
+      <c r="G15" s="2">
+        <v>43587</v>
       </c>
       <c r="H15">
         <v>184651</v>
@@ -1824,24 +1842,24 @@
         <v>55.27</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2">
         <v>44441</v>
@@ -1909,22 +1927,22 @@
         <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H17">
         <v>89135</v>
@@ -1989,22 +2007,22 @@
         <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H18">
         <v>98442</v>
@@ -2069,22 +2087,22 @@
         <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H19">
         <v>84574</v>
@@ -2149,19 +2167,19 @@
         <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" s="2">
         <v>44629</v>
@@ -2229,19 +2247,19 @@
         <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2">
         <v>45323</v>
@@ -2309,22 +2327,22 @@
         <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H22">
         <v>98</v>
@@ -2389,22 +2407,22 @@
         <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -2469,19 +2487,19 @@
         <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2">
         <v>45997</v>
@@ -2549,19 +2567,19 @@
         <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2">
         <v>45997</v>
@@ -2629,22 +2647,22 @@
         <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2698,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -2706,22 +2724,22 @@
         <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H27">
         <v>103706</v>
@@ -2786,19 +2804,19 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2">
         <v>45451</v>
@@ -2866,19 +2884,19 @@
         <v>83</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2">
         <v>45451</v>
@@ -2946,19 +2964,19 @@
         <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2">
         <v>45511</v>
@@ -3026,19 +3044,19 @@
         <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2">
         <v>45511</v>
@@ -3106,22 +3124,22 @@
         <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H32">
         <v>6877</v>
@@ -3186,22 +3204,22 @@
         <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H33">
         <v>68371</v>
@@ -3266,22 +3284,22 @@
         <v>88</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H34">
         <v>58515</v>
@@ -3346,22 +3364,22 @@
         <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H35">
         <v>54191</v>
